--- a/stories/arbres/TREE-TMP-004.xlsx
+++ b/stories/arbres/TREE-TMP-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est dans le train, avec papa. Les roues chantent. Papa dit : il y a douze mois. Un anniversaire a un mois. Inès écoute les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa dit : ton anniversaire a un mois. Inès pose la main sur le siège. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+          <t>Inès est dans le train, avec papa. Les roues chantent. Il y a douze mois. Un anniversaire a un mois. Inès écoute les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Ton anniversaire a un mois. Inès pose la main sur le siège. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est dans le train, avec papa. Les roues chantent.
+papa|Il y a douze mois.
+narrateur|Un anniversaire a un mois. Inès écoute les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.
+papa|Ton anniversaire a un mois.
+narrateur|Inès pose la main sur le siège. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès montre le train. Papa reprend les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois. Inès dit : janvier. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+          <t>Inès montre le train. Papa reprend les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois. Janvier. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1680,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre le train. Papa reprend les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois.
+enfant-f|Janvier. Il y a douze mois.
+narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Combien de mois ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a entendu les douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2229,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2398,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Tom. Le savon mousse entre les doigts. Tom écoute les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2589,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2756,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La lumière est claire. On referme le livre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2923,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3090,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On pose le ballon. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3257,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3424,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un chat miaule une fois. On secoue le sable. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3591,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3620,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès va vers Léa. La fenêtre vibre un peu. Léa dit : mon anniversaire. Papa ajoute : un mois, parmi les douze mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+          <t>Inès va vers Léa. La fenêtre vibre un peu. Mon anniversaire. Papa ajoute : un mois, parmi les douze mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3758,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Léa. La fenêtre vibre un peu.
+enfant-f|Mon anniversaire. Papa ajoute : un mois, parmi les douze mois. Il y a douze mois.
+narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Les chaussures font toc toc. On caresse le tissu. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Les chaussures font toc toc. On caresse le tissu. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Les chaussures font toc toc. On caresse le tissu. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La couverture est douce. On tend la main. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Une cloche tinte au loin. On chante un petit air. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Sami. Le sol est un peu frais. Sami compte. Douze. Les douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5312,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le bois sent le chaud. On compte jusqu'à trois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On montre du doigt. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon sent la fleur. On range la chaise. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inès montre le bus, en image. Douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa dit : un anniversaire a un mois. Inès dit : juin. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+          <t>Inès montre le bus, en image. Douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois. Juin. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6481,14 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre le bus, en image. Douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.
+papa|Un anniversaire a un mois.
+enfant-f|Juin. Il y a douze mois.
+narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6669,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|L'anniversaire a quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6842,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Douze mois. Inès a nommé un mois. L'anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6841,6 +7035,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7005,6 +7204,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Tom. L'eau fait un petit bruit. Inès et Tom tapent doucement. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7395,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7215,7 +7424,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Le tissu est tout doux. On range un objet. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Le tissu est tout doux. On range un objet. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7353,6 +7562,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le tissu est tout doux. On range un objet. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7730,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7897,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une cuillère tinte. On se tient la main. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8064,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8231,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le sable est tiède. On dit merci. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8398,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8565,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Léa. Le papier froisse, chut. Léa sourit. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Douze mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8756,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8923,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un rire court, tout petit. On souffle doucement. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9090,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9257,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On écoute jusqu'au bout. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9424,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9591,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On attend son tour. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9758,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9925,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Sami. La lumière est claire. Sami chuchote mai. Un mois. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10116,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9855,7 +10145,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Un pigeon roucoule. On sourit ensemble. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Un pigeon roucoule. On sourit ensemble. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9993,6 +10283,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un pigeon roucoule. On sourit ensemble. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On pose les pieds par terre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On parle tout bas. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11286,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre la voiture, en jouet. Les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a un mois. Inès sourit. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11467,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Janvier, c'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11640,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Papa confirme. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11497,6 +11833,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11661,6 +12002,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Tom. Une goutte tombe, ploc. Tom s'assoit. Papa dit encore : douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12193,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12360,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La corde du sac est rêche. On range les jouets. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12527,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12694,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On s'assoit un moment. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12861,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13028,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un ruisseau chante. On respire, un, deux. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13195,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13362,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Léa. Un rire court, tout petit. Léa range un crayon. Les douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13553,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13191,7 +13582,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. La laine gratte un peu. On referme le sac. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. La laine gratte un peu. On referme le sac. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13329,6 +13720,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La laine gratte un peu. On referme le sac. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13888,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14055,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Un pain croustille. On essuie une miette. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14222,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14389,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon glisse. On met le doudou près. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14556,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14723,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va vers Sami. La couverture est douce. Sami écoute jusqu'au bout. Douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14914,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15081,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Une plume vole. On lace les chaussures. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15248,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15415,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le banc est lisse. On met le manteau. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15582,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15749,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un grelot sonne. On boit une gorgée. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15916,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15508,6 +15970,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-004.xlsx
+++ b/stories/arbres/TREE-TMP-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1327,6 +1332,7 @@
 narrateur|Inès pose la main sur le siège. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
 narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Combien de mois ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Inès a entendu les douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2236,6 +2246,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2403,6 +2414,7 @@
           <t>narrateur|Inès va vers Tom. Le savon mousse entre les doigts. Tom écoute les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2594,6 +2606,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2774,7 @@
           <t>narrateur|Voilà le matin. La lumière est claire. On referme le livre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3095,6 +3110,7 @@
           <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On pose le ballon. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3262,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3429,6 +3446,7 @@
           <t>narrateur|Voilà le soir. Un chat miaule une fois. On secoue le sable. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3596,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
 narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Voilà après la sieste. La couverture est douce. On tend la main. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Voilà le soir. Une cloche tinte au loin. On chante un petit air. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Inès va vers Sami. Le sol est un peu frais. Sami compte. Douze. Les douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Voilà le matin. Le bois sent le chaud. On compte jusqu'à trois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On montre du doigt. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Voilà le soir. Le savon sent la fleur. On range la chaise. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6489,6 +6524,7 @@
 narrateur|Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6676,6 +6712,7 @@
           <t>narrateur|L'anniversaire a quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6847,6 +6884,7 @@
           <t>narrateur|Douze mois. Inès a nommé un mois. L'anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7042,6 +7080,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7209,6 +7248,7 @@
           <t>narrateur|Inès va vers Tom. L'eau fait un petit bruit. Inès et Tom tapent doucement. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7400,6 +7440,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7568,6 +7609,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7735,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7902,6 +7945,7 @@
           <t>narrateur|Voilà après la sieste. Une cuillère tinte. On se tient la main. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8069,6 +8113,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8236,6 +8281,7 @@
           <t>narrateur|Voilà le soir. Le sable est tiède. On dit merci. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8403,6 +8449,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8570,6 +8617,7 @@
           <t>narrateur|Inès va vers Léa. Le papier froisse, chut. Léa sourit. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Douze mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8761,6 +8809,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8928,6 +8977,7 @@
           <t>narrateur|Voilà le matin. Un rire court, tout petit. On souffle doucement. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9095,6 +9145,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9262,6 +9313,7 @@
           <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On écoute jusqu'au bout. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9429,6 +9481,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9596,6 +9649,7 @@
           <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On attend son tour. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9763,6 +9817,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9930,6 +9985,7 @@
           <t>narrateur|Inès va vers Sami. La lumière est claire. Sami chuchote mai. Un mois. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10121,6 +10177,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On pose les pieds par terre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On parle tout bas. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11291,6 +11354,7 @@
           <t>narrateur|Inès montre la voiture, en jouet. Les douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a un mois. Inès sourit. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11474,6 +11538,7 @@
           <t>narrateur|Janvier, c'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11645,6 +11710,7 @@
           <t>narrateur|Papa confirme. Douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11840,6 +11906,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12007,6 +12074,7 @@
           <t>narrateur|Inès va vers Tom. Une goutte tombe, ploc. Tom s'assoit. Papa dit encore : douze mois. Un anniversaire a un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12198,6 +12266,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12365,6 +12434,7 @@
           <t>narrateur|Voilà le matin. La corde du sac est rêche. On range les jouets. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12532,6 +12602,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12699,6 +12770,7 @@
           <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On s'assoit un moment. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12866,6 +12938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13033,6 +13106,7 @@
           <t>narrateur|Voilà le soir. Un ruisseau chante. On respire, un, deux. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13200,6 +13274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13367,6 +13442,7 @@
           <t>narrateur|Inès va vers Léa. Un rire court, tout petit. Léa range un crayon. Les douze mois. Anniversaire. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13558,6 +13634,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13726,6 +13803,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13893,6 +13971,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14060,6 +14139,7 @@
           <t>narrateur|Voilà après la sieste. Un pain croustille. On essuie une miette. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On souffle. Inès sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14227,6 +14307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14394,6 +14475,7 @@
           <t>narrateur|Voilà le soir. Le savon glisse. On met le doudou près. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Les douze mois sont dits. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14561,6 +14643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14728,6 +14811,7 @@
           <t>narrateur|Inès va vers Sami. La couverture est douce. Sami écoute jusqu'au bout. Douze mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14919,6 +15003,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15086,6 +15171,7 @@
           <t>narrateur|Voilà le matin. Une plume vole. On lace les chaussures. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. On a nommé un mois. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Inès dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15253,6 +15339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15420,6 +15507,7 @@
           <t>narrateur|Voilà après la sieste. Le banc est lisse. On met le manteau. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. L'anniversaire a sa place. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Papa serre Inès tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15587,6 +15675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15754,6 +15843,7 @@
           <t>narrateur|Voilà le soir. Un grelot sonne. On boit une gorgée. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Le train continue. Il y a douze mois. Un anniversaire a un mois. Janvier, février, mars, avril, mai, juin, juillet, août, septembre, octobre, novembre, décembre. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15921,6 +16011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15939,7 +16030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15977,6 +16068,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15991,7 +16096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16178,6 +16283,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
